--- a/ALL/p12-out/Recipes.xlsx
+++ b/ALL/p12-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Title</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Generated At</t>
+  </si>
+  <si>
+    <t>Json Recipe</t>
   </si>
   <si>
     <t>Chocolate Banana Pancakes</t>
@@ -94,6 +97,173 @@
   </si>
   <si>
     <t>2026-04-30 07:25:29</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Chocolate Banana Pancakes",
+  "summary": "Delicious and fluffy pancakes infused with chocolate and ripe bananas, perfect for breakfast. Serve warm with chocolate chips and banana slices.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "15",
+  "total_time": "25",
+  "calories": "250",
+  "course": "Breakfast",
+  "cuisine": "American",
+  "keywords": [
+    "pancakes",
+    "chocolate",
+    "banana",
+    "breakfast",
+    "easy"
+  ],
+  "notes": "For extra flavor, add nuts or spices like cinnamon. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "2",
+      "unit": "",
+      "name": "ripe bananas, mashed"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "cocoa powder"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "sugar"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "baking powder"
+    },
+    {
+      "amount": "½",
+      "unit": "teaspoon",
+      "name": "baking soda"
+    },
+    {
+      "amount": "¼",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "milk"
+    },
+    {
+      "amount": "1",
+      "unit": "large",
+      "name": "egg"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "melted butter"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Chocolate chips for topping (optional)"
+    }
+  ],
+  "instructions": [
+    "In a large bowl, whisk together the flour, cocoa powder, sugar, baking powder, baking soda, and salt.",
+    "In another bowl, combine the mashed bananas, milk, egg, and melted butter, mixing until well combined.",
+    "Pour the wet ingredients into the dry ingredients and stir gently until just combined; do not overmix.",
+    "Preheat a non-stick skillet or griddle over medium heat and lightly grease with cooking spray or butter.",
+    "Pour ¼ cup of batter onto the skillet for each pancake and cook until bubbles form on the surface, about 2-3 minutes.",
+    "Flip the pancakes and cook for an additional 1-2 minutes until cooked through and slightly golden.",
+    "Remove from the skillet and keep warm while you repeat with the remaining batter.",
+    "Serve pancakes warm topped with chocolate chips and additional banana slices if desired."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Classic Vegetable Stir Fry",
+  "summary": "A quick and colorful stir fry featuring a mix of fresh vegetables, perfect for a healthy meal. Serve it over rice or noodles for a satisfying dish.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "10",
+  "total_time": "20",
+  "calories": "250",
+  "course": "Main Course",
+  "cuisine": "Asian",
+  "keywords": [
+    "vegetable",
+    "stir fry",
+    "quick",
+    "healthy",
+    "Asian",
+    "easy",
+    "dinner"
+  ],
+  "notes": "Feel free to customize the vegetable mix based on your preferences. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "mixed vegetables (bell peppers, broccoli, carrots, snap peas)"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "vegetable oil"
+    },
+    {
+      "amount": "3",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "1",
+      "unit": "inch",
+      "name": "ginger, grated"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "soy sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "sesame oil"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "cornstarch mixed with 2 tablespoons water (for thickening)"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Cooked rice or noodles, for serving"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Sesame seeds and green onions for garnish"
+    }
+  ],
+  "instructions": [
+    "Heat the vegetable oil in a large skillet or wok over medium-high heat.",
+    "Add the minced garlic and grated ginger, sautéing for about 30 seconds until fragrant.",
+    "Add the mixed vegetables to the skillet and stir-fry for 4-5 minutes until they are tender yet crisp.",
+    "Pour in the soy sauce and sesame oil, stirring to coat the vegetables evenly.",
+    "Add the cornstarch mixture to the pan and cook for an additional 1-2 minutes until the sauce thickens.",
+    "Remove from heat and serve the stir-fry over cooked rice or noodles.",
+    "Garnish with sesame seeds and sliced green onions before serving."
+  ]
+}</t>
   </si>
 </sst>
 </file>
@@ -451,10 +621,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,27 +634,36 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/ALL/p12-out/Recipes.xlsx
+++ b/ALL/p12-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Title</t>
   </si>
@@ -28,242 +28,251 @@
     <t>Json Recipe</t>
   </si>
   <si>
-    <t>Chocolate Banana Pancakes</t>
-  </si>
-  <si>
-    <t>Classic Vegetable Stir Fry</t>
-  </si>
-  <si>
-    <t>Chocolate Banana Pancakes 🍌🍫
+    <t>Prompt</t>
+  </si>
+  <si>
+    <t>Prompt Image Ingredients</t>
+  </si>
+  <si>
+    <t>One-Pan Honey Butter Salmon &amp; Rice</t>
+  </si>
+  <si>
+    <t>Juicy Air Fryer BBQ Chicken Bites</t>
+  </si>
+  <si>
+    <t>One-Pan Honey Butter Salmon &amp; Rice 🍯🐟
 Ingredients:
-- 1 cup all-purpose flour
-- 2 ripe bananas, mashed
-- 2 tablespoons cocoa powder
-- 2 tablespoons sugar
-- 1 teaspoon baking powder
-- 1/2 teaspoon baking soda
-- 1/4 teaspoon salt
-- 1 cup milk
-- 1 large egg
-- 2 tablespoons melted butter
-- Chocolate chips for topping (optional)
+- 2 salmon fillets
+- 1 cup jasmine rice
+- 2 cups vegetable broth
+- 3 tablespoons honey
+- 2 tablespoons unsalted butter
+- 1 tablespoon soy sauce
+- 2 cloves garlic, minced
+- 1 teaspoon fresh ginger, grated
+- Salt and pepper to taste
+- 2 green onions, sliced (for garnish)
 Instructions:
-1. In a large bowl, whisk together the flour, cocoa powder, sugar, baking powder, baking soda, and salt.
-2. In another bowl, combine the mashed bananas, milk, egg, and melted butter, mixing until well combined.
-3. Pour the wet ingredients into the dry ingredients and stir gently until just combined; do not overmix.
-4. Preheat a non-stick skillet or griddle over medium heat and lightly grease with cooking spray or butter.
-5. Pour 1/4 cup of batter onto the skillet for each pancake and cook until bubbles form on the surface, about 2-3 minutes.
-6. Flip the pancakes and cook for an additional 1-2 minutes until cooked through and slightly golden.
-7. Remove from the skillet and keep warm while you repeat with the remaining batter.
-8. Serve pancakes warm topped with chocolate chips and additional banana slices if desired.
+1. In a large skillet, melt the butter over medium heat.
+2. Add the minced garlic and grated ginger, sautéing until fragrant, about 1 minute.
+3. Stir in the honey and soy sauce, mixing well to create a glaze.
+4. Push the garlic mixture to the side of the skillet and place the salmon fillets skin-side down in the pan.
+5. Season the salmon with salt and pepper, then cook for 3-4 minutes until slightly browned.
+6. Add the jasmine rice to the skillet, followed by the vegetable broth. Bring to a simmer.
+7. Cover the skillet and reduce the heat to low, cooking for 15-18 minutes or until the rice is tender and the salmon is cooked through.
+8. Remove from heat and let it sit covered for 5 minutes.
+9. Fluff the rice with a fork and drizzle any remaining honey butter glaze over the salmon.
+10. Garnish with sliced green onions before serving.
 Prep Time: 10 minutes
-Cook Time: 15 minutes
-Total Time: 25 minutes
-Course: Breakfast
+Cook Time: 25 minutes
+Total Time: 35 minutes
+Course: Main Course
+Cuisine: Asian-inspired
+Servings: 2
+Calories: ~450 per serving</t>
+  </si>
+  <si>
+    <t>Juicy Air Fryer BBQ Chicken Bites 🍗🔥
+Ingredients:
+- 1 pound chicken breast, cut into bite-sized pieces
+- 1 cup barbecue sauce
+- 1 tablespoon olive oil
+- 1 teaspoon garlic powder
+- 1 teaspoon onion powder
+- Salt and pepper to taste
+- Fresh parsley for garnish (optional)
+Instructions:
+1. In a mixing bowl, combine the chicken pieces with olive oil, garlic powder, onion powder, salt, and pepper. Toss until the chicken is evenly coated.
+2. Add the barbecue sauce to the chicken and mix until all pieces are well coated.
+3. Preheat the air fryer to 400°F (200°C) for about 5 minutes.
+4. Place the sauced chicken bites in a single layer in the air fryer basket, making sure they are not overcrowded.
+5. Cook the chicken bites in the air fryer for 10-12 minutes, shaking the basket halfway through to ensure even cooking.
+6. Check the internal temperature of the chicken; it should reach 165°F (75°C).
+7. Once cooked, remove the chicken bites from the air fryer and let them rest for a few minutes.
+8. Garnish with fresh parsley if desired and serve with extra barbecue sauce on the side.
+Prep Time: 10 minutes
+Cook Time: 12 minutes
+Total Time: 22 minutes
+Course: Appetizer/Main Dish
 Cuisine: American
 Servings: 4
 Calories: ~250 per serving</t>
   </si>
   <si>
-    <t>Classic Vegetable Stir Fry 🥦🍚
-Ingredients:
-- 2 cups mixed vegetables (bell peppers, broccoli, carrots, snap peas)
-- 2 tablespoons vegetable oil
-- 3 cloves garlic, minced
-- 1 inch ginger, grated
-- 2 tablespoons soy sauce
-- 1 tablespoon sesame oil
-- 1 tablespoon cornstarch mixed with 2 tablespoons water (for thickening)
-- Cooked rice or noodles, for serving
-- Sesame seeds and green onions for garnish
-Instructions:
-1. Heat the vegetable oil in a large skillet or wok over medium-high heat.
-2. Add the minced garlic and grated ginger, sautéing for about 30 seconds until fragrant.
-3. Add the mixed vegetables to the skillet and stir-fry for 4-5 minutes until they are tender yet crisp.
-4. Pour in the soy sauce and sesame oil, stirring to coat the vegetables evenly.
-5. Add the cornstarch mixture to the pan and cook for an additional 1-2 minutes until the sauce thickens.
-6. Remove from heat and serve the stir-fry over cooked rice or noodles.
-7. Garnish with sesame seeds and sliced green onions before serving.
-Prep Time: 10 minutes
-Cook Time: 10 minutes
-Total Time: 20 minutes
-Course: Main Course
-Cuisine: Asian
-Servings: 4
-Calories: ~250 per serving</t>
-  </si>
-  <si>
-    <t>2026-04-30 07:13:04</t>
-  </si>
-  <si>
-    <t>2026-04-30 07:25:29</t>
+    <t>2026-05-08 14:43:16</t>
+  </si>
+  <si>
+    <t>2026-05-08 14:43:25</t>
   </si>
   <si>
     <t>{
-  "name": "Chocolate Banana Pancakes",
-  "summary": "Delicious and fluffy pancakes infused with chocolate and ripe bananas, perfect for breakfast. Serve warm with chocolate chips and banana slices.",
-  "servings": "4",
+  "name": "One-Pan Honey Butter Salmon &amp; Rice",
+  "summary": "This dish features succulent salmon fillets cooked in a sweet honey butter glaze, served over fluffy jasmine rice. It's a quick and flavorful meal made in one pan.",
+  "servings": "2",
   "prep_time": "10",
-  "cook_time": "15",
-  "total_time": "25",
-  "calories": "250",
-  "course": "Breakfast",
-  "cuisine": "American",
+  "cook_time": "25",
+  "total_time": "35",
+  "calories": "450",
+  "course": "Main Course",
+  "cuisine": "Asian",
   "keywords": [
-    "pancakes",
-    "chocolate",
-    "banana",
-    "breakfast",
-    "easy"
+    "salmon",
+    "honey",
+    "butter",
+    "rice",
+    "one-pan",
+    "easy",
+    "dinner"
   ],
-  "notes": "For extra flavor, add nuts or spices like cinnamon. Calories are per serving.",
+  "notes": "Let the dish sit covered for a few minutes after cooking for best results. Calories are per serving.",
   "ingredients": [
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "all-purpose flour"
-    },
     {
       "amount": "2",
       "unit": "",
-      "name": "ripe bananas, mashed"
+      "name": "salmon fillets"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "jasmine rice"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "vegetable broth"
+    },
+    {
+      "amount": "3",
+      "unit": "tablespoons",
+      "name": "honey"
     },
     {
       "amount": "2",
       "unit": "tablespoons",
-      "name": "cocoa powder"
+      "name": "unsalted butter"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "soy sauce"
     },
     {
       "amount": "2",
-      "unit": "tablespoons",
-      "name": "sugar"
+      "unit": "cloves",
+      "name": "garlic, minced"
     },
     {
       "amount": "1",
       "unit": "teaspoon",
-      "name": "baking powder"
-    },
-    {
-      "amount": "½",
-      "unit": "teaspoon",
-      "name": "baking soda"
-    },
-    {
-      "amount": "¼",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "milk"
-    },
-    {
-      "amount": "1",
-      "unit": "large",
-      "name": "egg"
-    },
-    {
-      "amount": "2",
-      "unit": "tablespoons",
-      "name": "melted butter"
+      "name": "fresh ginger, grated"
     },
     {
       "amount": "",
       "unit": "",
-      "name": "Chocolate chips for topping (optional)"
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "2",
+      "unit": "",
+      "name": "green onions, sliced (for garnish)"
     }
   ],
   "instructions": [
-    "In a large bowl, whisk together the flour, cocoa powder, sugar, baking powder, baking soda, and salt.",
-    "In another bowl, combine the mashed bananas, milk, egg, and melted butter, mixing until well combined.",
-    "Pour the wet ingredients into the dry ingredients and stir gently until just combined; do not overmix.",
-    "Preheat a non-stick skillet or griddle over medium heat and lightly grease with cooking spray or butter.",
-    "Pour ¼ cup of batter onto the skillet for each pancake and cook until bubbles form on the surface, about 2-3 minutes.",
-    "Flip the pancakes and cook for an additional 1-2 minutes until cooked through and slightly golden.",
-    "Remove from the skillet and keep warm while you repeat with the remaining batter.",
-    "Serve pancakes warm topped with chocolate chips and additional banana slices if desired."
+    "In a large skillet, melt the butter over medium heat.",
+    "Add the minced garlic and grated ginger, sautéing until fragrant, about 1 minute.",
+    "Stir in the honey and soy sauce, mixing well to create a glaze.",
+    "Push the garlic mixture to the side of the skillet and place the salmon fillets skin-side down in the pan.",
+    "Season the salmon with salt and pepper, then cook for 3-4 minutes until slightly browned.",
+    "Add the jasmine rice to the skillet, followed by the vegetable broth. Bring to a simmer.",
+    "Cover the skillet and reduce the heat to low, cooking for 15-18 minutes or until the rice is tender and the salmon is cooked through.",
+    "Remove from heat and let it sit covered for 5 minutes.",
+    "Fluff the rice with a fork and drizzle any remaining honey butter glaze over the salmon.",
+    "Garnish with sliced green onions before serving."
   ]
 }</t>
   </si>
   <si>
     <t>{
-  "name": "Classic Vegetable Stir Fry",
-  "summary": "A quick and colorful stir fry featuring a mix of fresh vegetables, perfect for a healthy meal. Serve it over rice or noodles for a satisfying dish.",
+  "name": "Juicy Air Fryer BBQ Chicken Bites",
+  "summary": "These Juicy Air Fryer BBQ Chicken Bites are tender, flavorful, and coated in a delicious barbecue sauce. Perfect as an appetizer or main dish, they are quick and easy to prepare.",
   "servings": "4",
   "prep_time": "10",
-  "cook_time": "10",
-  "total_time": "20",
+  "cook_time": "12",
+  "total_time": "22",
   "calories": "250",
-  "course": "Main Course",
-  "cuisine": "Asian",
+  "course": "Appetizer",
+  "cuisine": "American",
   "keywords": [
-    "vegetable",
-    "stir fry",
+    "chicken",
+    "air fryer",
+    "bbq",
+    "appetizer",
+    "easy",
     "quick",
-    "healthy",
-    "Asian",
-    "easy",
-    "dinner"
+    "tender"
   ],
-  "notes": "Feel free to customize the vegetable mix based on your preferences. Calories are per serving.",
+  "notes": "Ensure chicken reaches an internal temperature of 165°F for safety. Calories are per serving.",
   "ingredients": [
     {
-      "amount": "2",
-      "unit": "cups",
-      "name": "mixed vegetables (bell peppers, broccoli, carrots, snap peas)"
-    },
-    {
-      "amount": "2",
-      "unit": "tablespoons",
-      "name": "vegetable oil"
-    },
-    {
-      "amount": "3",
-      "unit": "cloves",
-      "name": "garlic, minced"
-    },
-    {
-      "amount": "1",
-      "unit": "inch",
-      "name": "ginger, grated"
-    },
-    {
-      "amount": "2",
-      "unit": "tablespoons",
-      "name": "soy sauce"
+      "amount": "1",
+      "unit": "pound",
+      "name": "chicken breast, cut into bite-sized pieces"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "barbecue sauce"
     },
     {
       "amount": "1",
       "unit": "tablespoon",
-      "name": "sesame oil"
-    },
-    {
-      "amount": "1",
-      "unit": "tablespoon",
-      "name": "cornstarch mixed with 2 tablespoons water (for thickening)"
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "onion powder"
     },
     {
       "amount": "",
       "unit": "",
-      "name": "Cooked rice or noodles, for serving"
+      "name": "Salt and pepper to taste"
     },
     {
       "amount": "",
       "unit": "",
-      "name": "Sesame seeds and green onions for garnish"
+      "name": "Fresh parsley for garnish (optional)"
     }
   ],
   "instructions": [
-    "Heat the vegetable oil in a large skillet or wok over medium-high heat.",
-    "Add the minced garlic and grated ginger, sautéing for about 30 seconds until fragrant.",
-    "Add the mixed vegetables to the skillet and stir-fry for 4-5 minutes until they are tender yet crisp.",
-    "Pour in the soy sauce and sesame oil, stirring to coat the vegetables evenly.",
-    "Add the cornstarch mixture to the pan and cook for an additional 1-2 minutes until the sauce thickens.",
-    "Remove from heat and serve the stir-fry over cooked rice or noodles.",
-    "Garnish with sesame seeds and sliced green onions before serving."
+    "In a mixing bowl, combine the chicken pieces with olive oil, garlic powder, onion powder, salt, and pepper.",
+    "Toss until the chicken is evenly coated.",
+    "Add the barbecue sauce to the chicken and mix until all pieces are well coated.",
+    "Preheat the air fryer to 400°F (200°C) for about 5 minutes.",
+    "Place the sauced chicken bites in a single layer in the air fryer basket.",
+    "Cook the chicken bites in the air fryer for 10-12 minutes, shaking the basket halfway through.",
+    "Check the internal temperature of the chicken; it should reach 165°F (75°C).",
+    "Once cooked, remove the chicken bites from the air fryer and let them rest for a few minutes.",
+    "Garnish with fresh parsley if desired and serve with extra barbecue sauce on the side."
   ]
 }</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a beautifully plated One-Pan Honey Butter Salmon &amp; Rice dish, featuring a perfectly cooked salmon fillet glazed with honey butter, nestled on a bed of fluffy jasmine rice, garnished with sliced green onions. Serve in a clean white ceramic bowl on a light neutral surface, tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of juicy air fryer BBQ chicken bites, glistening with barbecue sauce, served in a clean white ceramic bowl on a light neutral surface. The chicken pieces are garnished with fresh parsley, showcasing clear food texture and vibrant colors, with soft natural daylight creating gentle shadows. The composition fills 90–100% of the frame, with sharp focus on the center of the dish at a slight eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>salmon, jasmine rice, vegetable broth, honey, butter, soy sauce, garlic, ginger, green onions, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>chicken, barbecue sauce, olive oil, garlic powder, onion powder, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
   </si>
 </sst>
 </file>
@@ -621,10 +630,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,33 +646,51 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/ALL/p12-out/Recipes.xlsx
+++ b/ALL/p12-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="144">
   <si>
     <t>Title</t>
   </si>
@@ -34,10 +34,106 @@
     <t>Prompt Image Ingredients</t>
   </si>
   <si>
+    <t>main_image</t>
+  </si>
+  <si>
+    <t>image_1</t>
+  </si>
+  <si>
+    <t>image_2</t>
+  </si>
+  <si>
+    <t>image_3</t>
+  </si>
+  <si>
+    <t>image_4</t>
+  </si>
+  <si>
+    <t>statu</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>main_image_ingredients</t>
+  </si>
+  <si>
+    <t>image_ing_1</t>
+  </si>
+  <si>
+    <t>image_ing_2</t>
+  </si>
+  <si>
+    <t>image_ing_3</t>
+  </si>
+  <si>
+    <t>image_ing_4</t>
+  </si>
+  <si>
+    <t>statu_ing</t>
+  </si>
+  <si>
+    <t>error_ing</t>
+  </si>
+  <si>
+    <t>Statut Article</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>article_title</t>
+  </si>
+  <si>
+    <t>id_article</t>
+  </si>
+  <si>
+    <t>pinterest_title</t>
+  </si>
+  <si>
+    <t>recipe_title_pin</t>
+  </si>
+  <si>
+    <t>pinterest_description</t>
+  </si>
+  <si>
+    <t>pinterest_keywords</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_focuskw</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_metadesc</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_keywordsynonyms</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>pinterest_image</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>post_url</t>
+  </si>
+  <si>
     <t>One-Pan Honey Butter Salmon &amp; Rice</t>
   </si>
   <si>
     <t>Juicy Air Fryer BBQ Chicken Bites</t>
+  </si>
+  <si>
+    <t>Healthy Greek Chicken Bowls</t>
+  </si>
+  <si>
+    <t>Soft &amp; Fluffy Homemade Cinnamon Rolls</t>
   </si>
   <si>
     <t>One-Pan Honey Butter Salmon &amp; Rice 🍯🐟
@@ -99,15 +195,88 @@
 Calories: ~250 per serving</t>
   </si>
   <si>
+    <t>Healthy Greek Chicken Bowls 🇬🇷🥗
+Ingredients:
+- 2 boneless, skinless chicken breasts
+- 1 cup quinoa, rinsed
+- 1 tablespoon olive oil
+- 1 teaspoon dried oregano
+- 1 teaspoon garlic powder
+- Salt and pepper to taste
+- 1 cup cherry tomatoes, halved
+- 1 cucumber, diced
+- 1/2 red onion, thinly sliced
+- 1/2 cup feta cheese, crumbled
+- 1/4 cup Kalamata olives, pitted and halved
+- Fresh parsley for garnish
+Instructions:
+1. Preheat your oven to 400°F (200°C).
+2. In a small bowl, mix olive oil, oregano, garlic powder, salt, and pepper. Rub this mixture onto the chicken breasts.
+3. Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through and juices run clear.
+4. While the chicken is baking, cook the quinoa according to package instructions. Fluff with a fork once done.
+5. In a large bowl, combine cherry tomatoes, cucumber, red onion, feta cheese, and Kalamata olives. Toss gently to mix.
+6. Once the chicken is cooked, let it rest for a few minutes, then slice it into strips.
+7. To assemble the bowls, start with a base of quinoa, top with the veggie mixture, and add sliced chicken on top.
+8. Garnish with fresh parsley before serving.
+Prep Time: 15 minutes
+Cook Time: 25 minutes
+Total Time: 40 minutes
+Course: Main Course
+Cuisine: Greek
+Servings: 4
+Calories: ~450 per serving</t>
+  </si>
+  <si>
+    <t>Soft &amp; Fluffy Homemade Cinnamon Rolls 🍩✨
+Ingredients:
+- 4 cups all-purpose flour
+- 1 cup warm milk (110°F)
+- 1/2 cup granulated sugar
+- 1/4 cup unsalted butter, melted
+- 2 large eggs
+- 1 packet (2 1/4 tsp) active dry yeast
+- 1 teaspoon salt
+- 1 tablespoon ground cinnamon
+- 1/2 cup packed brown sugar
+- 1/4 cup cream cheese, softened
+- 1 cup powdered sugar
+- 2 tablespoons milk (for icing)
+Instructions:
+1. In a small bowl, combine warm milk and yeast. Let sit for 5-10 minutes until frothy.
+2. In a large mixing bowl, whisk together flour, sugar, and salt.
+3. Add the melted butter, eggs, and the yeast mixture to the dry ingredients. Mix until a dough forms.
+4. Knead the dough on a floured surface for about 5-7 minutes until smooth and elastic.
+5. Place the dough in a greased bowl, cover with a cloth, and let it rise in a warm place for 1 hour or until doubled in size.
+6. Once risen, roll out the dough into a rectangle about 1/4 inch thick.
+7. Spread softened butter over the dough, then sprinkle with brown sugar and cinnamon.
+8. Roll the dough tightly from the long side and cut into 12 equal pieces.
+9. Place the rolls in a greased baking dish and let them rise for another 30 minutes.
+10. Preheat the oven to 350°F (175°C) and bake the rolls for 20-25 minutes until golden brown.
+11. While the rolls are baking, mix cream cheese, powdered sugar, and milk to create the icing. Drizzle over warm rolls before serving.
+Prep Time: 30 minutes
+Cook Time: 25 minutes
+Total Time: 1 hour 55 minutes
+Course: Breakfast/Dessert
+Cuisine: American
+Servings: 12
+Calories: ~250 per roll</t>
+  </si>
+  <si>
     <t>2026-05-08 14:43:16</t>
   </si>
   <si>
     <t>2026-05-08 14:43:25</t>
+  </si>
+  <si>
+    <t>2026-05-08 21:36:03</t>
+  </si>
+  <si>
+    <t>2026-05-08 21:36:14</t>
   </si>
   <si>
     <t>{
   "name": "One-Pan Honey Butter Salmon &amp; Rice",
-  "summary": "This dish features succulent salmon fillets cooked in a sweet honey butter glaze, served over fluffy jasmine rice. It's a quick and flavorful meal made in one pan.",
+  "summary": "This delicious one-pan dish features salmon fillets cooked in a honey butter glaze served over jasmine rice. It's a quick and flavorful meal perfect for any night.",
   "servings": "2",
   "prep_time": "10",
   "cook_time": "25",
@@ -117,12 +286,10 @@
   "cuisine": "Asian",
   "keywords": [
     "salmon",
-    "honey",
-    "butter",
     "rice",
+    "honey butter",
     "one-pan",
-    "easy",
-    "dinner"
+    "quick meal"
   ],
   "notes": "Let the dish sit covered for a few minutes after cooking for best results. Calories are per serving.",
   "ingredients": [
@@ -194,7 +361,7 @@
   <si>
     <t>{
   "name": "Juicy Air Fryer BBQ Chicken Bites",
-  "summary": "These Juicy Air Fryer BBQ Chicken Bites are tender, flavorful, and coated in a delicious barbecue sauce. Perfect as an appetizer or main dish, they are quick and easy to prepare.",
+  "summary": "These Juicy Air Fryer BBQ Chicken Bites are a quick and delicious appetizer or main dish, perfect for any gathering. Coated in barbecue sauce and seasoned to perfection, they're sure to be a hit.",
   "servings": "4",
   "prep_time": "10",
   "cook_time": "12",
@@ -203,13 +370,12 @@
   "course": "Appetizer",
   "cuisine": "American",
   "keywords": [
+    "air fryer",
     "chicken",
-    "air fryer",
     "bbq",
     "appetizer",
-    "easy",
     "quick",
-    "tender"
+    "easy"
   ],
   "notes": "Ensure chicken reaches an internal temperature of 165°F for safety. Calories are per serving.",
   "ingredients": [
@@ -263,23 +429,869 @@
 }</t>
   </si>
   <si>
-    <t>Realistic, appetizing ULTRA close-up of a beautifully plated One-Pan Honey Butter Salmon &amp; Rice dish, featuring a perfectly cooked salmon fillet glazed with honey butter, nestled on a bed of fluffy jasmine rice, garnished with sliced green onions. Serve in a clean white ceramic bowl on a light neutral surface, tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>Realistic, appetizing ULTRA close-up of juicy air fryer BBQ chicken bites, glistening with barbecue sauce, served in a clean white ceramic bowl on a light neutral surface. The chicken pieces are garnished with fresh parsley, showcasing clear food texture and vibrant colors, with soft natural daylight creating gentle shadows. The composition fills 90–100% of the frame, with sharp focus on the center of the dish at a slight eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>salmon, jasmine rice, vegetable broth, honey, butter, soy sauce, garlic, ginger, green onions, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+    <t>{
+  "name": "Healthy Greek Chicken Bowls",
+  "summary": "These Healthy Greek Chicken Bowls are a nutritious and flavorful meal featuring baked chicken, quinoa, and fresh vegetables. Perfect for a wholesome dinner or lunch.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "25",
+  "total_time": "40",
+  "calories": "450",
+  "course": "Main Course",
+  "cuisine": "Greek",
+  "keywords": [
+    "chicken",
+    "quinoa",
+    "healthy",
+    "Greek",
+    "bowl",
+    "meal"
+  ],
+  "notes": "Feel free to customize the veggies based on your preference. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "2",
+      "unit": "pieces",
+      "name": "boneless, skinless chicken breasts"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "quinoa, rinsed"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "dried oregano"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "garlic powder"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "cherry tomatoes, halved"
+    },
+    {
+      "amount": "1",
+      "unit": "piece",
+      "name": "cucumber, diced"
+    },
+    {
+      "amount": "½",
+      "unit": "piece",
+      "name": "red onion, thinly sliced"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "feta cheese, crumbled"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "Kalamata olives, pitted and halved"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh parsley for garnish"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 400°F (200°C).",
+    "In a small bowl, mix olive oil, oregano, garlic powder, salt, and pepper. Rub this mixture onto the chicken breasts.",
+    "Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through and juices run clear.",
+    "While the chicken is baking, cook the quinoa according to package instructions. Fluff with a fork once done.",
+    "In a large bowl, combine cherry tomatoes, cucumber, red onion, feta cheese, and Kalamata olives. Toss gently to mix.",
+    "Once the chicken is cooked, let it rest for a few minutes, then slice it into strips.",
+    "To assemble the bowls, start with a base of quinoa, top with the veggie mixture, and add sliced chicken on top.",
+    "Garnish with fresh parsley before serving."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Soft &amp; Fluffy Homemade Cinnamon Rolls",
+  "summary": "These cinnamon rolls are soft, fluffy, and topped with a creamy icing, making them perfect for breakfast or dessert. Enjoy the delightful combination of cinnamon and sugar in every bite.",
+  "servings": "12",
+  "prep_time": "30",
+  "cook_time": "25",
+  "total_time": "115",
+  "calories": "250",
+  "course": "Breakfast",
+  "cuisine": "American",
+  "keywords": [
+    "cinnamon rolls",
+    "homemade",
+    "breakfast",
+    "dessert",
+    "baking"
+  ],
+  "notes": "For best results, ensure the milk is warm but not hot when activating the yeast. Calories are per roll.",
+  "ingredients": [
+    {
+      "amount": "4",
+      "unit": "cups",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "warm milk"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "granulated sugar"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "unsalted butter, melted"
+    },
+    {
+      "amount": "2",
+      "unit": "large",
+      "name": "eggs"
+    },
+    {
+      "amount": "1",
+      "unit": "packet (2 ¼ tsp)",
+      "name": "active dry yeast"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "ground cinnamon"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "packed brown sugar"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "cream cheese, softened"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "powdered sugar"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "milk (for icing)"
+    }
+  ],
+  "instructions": [
+    "In a small bowl, combine warm milk and yeast. Let sit for 5-10 minutes until frothy.",
+    "In a large mixing bowl, whisk together flour, sugar, and salt.",
+    "Add the melted butter, eggs, and the yeast mixture to the dry ingredients. Mix until a dough forms.",
+    "Knead the dough on a floured surface for about 5-7 minutes until smooth and elastic.",
+    "Place the dough in a greased bowl, cover with a cloth, and let it rise in a warm place for 60 minutes or until doubled in size.",
+    "Once risen, roll out the dough into a rectangle about ¼ inch thick.",
+    "Spread softened butter over the dough, then sprinkle with brown sugar and cinnamon.",
+    "Roll the dough tightly from the long side and cut into 12 equal pieces.",
+    "Place the rolls in a greased baking dish and let them rise for another 30 minutes.",
+    "Preheat the oven to 350°F and bake the rolls for 20-25 minutes until golden brown.",
+    "While the rolls are baking, mix cream cheese, powdered sugar, and milk to create the icing. Drizzle over warm rolls before serving."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a beautifully plated one-pan honey butter salmon and rice dish in a clean white ceramic bowl, featuring two perfectly cooked salmon fillets glistening with honey glaze, fluffy jasmine rice, and garnished with vibrant green onion slices, all on a light neutral surface. The composition fills 90–100% of the frame with clear food texture, soft natural daylight creating gentle shadows, sharp focus at the food center, and a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of juicy air fryer BBQ chicken bites, glistening with barbecue sauce, served in a clean white ceramic bowl, garnished with fresh parsley, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the chicken bites, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Ultra close-up of a healthy Greek chicken bowl featuring sliced grilled chicken breast on a bed of fluffy quinoa, vibrant cherry tomatoes, diced cucumber, thinly sliced red onion, crumbled feta cheese, and Kalamata olives, all garnished with fresh parsley, served in a clean white ceramic bowl on a light neutral surface, soft natural daylight illuminating the dish, shallow depth of field, sharp focus on the center, slight 3/4 angle composition , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of soft and fluffy homemade cinnamon rolls drizzled with cream cheese icing, served in a clean white ceramic plate, on a light neutral surface. Tight composition filling 90–100% of frame, showcasing the texture of the rolls and icing, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the rolls, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>salmon, jasmine rice, vegetable broth, honey, unsalted butter, soy sauce, garlic, ginger, salt, pepper, green onions, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
   </si>
   <si>
     <t>chicken, barbecue sauce, olive oil, garlic powder, onion powder, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>chicken, quinoa, olive oil, oregano, garlic powder, salt, pepper, cherry tomatoes, cucumber, red onion, feta cheese, Kalamata olives, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>flour, milk, sugar, butter, eggs, yeast, salt, cinnamon, brown sugar, cream cheese, powdered sugar, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509095/2545fe630aa.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509095/cd37fd6c5a6.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509095/39123f8aadb.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509095/8f6475ce5bb.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/669e3f9fd7c.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/49228e06cf6.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/ef26d2f1726.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/e9e7e9009b7.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/c87f31864eb.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/43abe5f7089.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/76273d198f9.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/57df8079b9d.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/783636737d7.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/a3c4255691a.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/ad2eb61a76f.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/c9073ba50ee.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/5e38231b741.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/09e40ab3381.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/b5c1c42fa87.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509095/87135835e6e.png</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509095/7c1f255edb4.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509095/fec1ad04ade.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509095/b3bfd5ce48f.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509095/923c057dadf.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/87d3ff787c8.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/293bf1411f7.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/59b974a46c6.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/d5b994915fe.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/c4662f84e55.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/ba423a529fd.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/9296eea1b20.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/f912c5d8a07.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/b8a6a03d432.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/14919d46933.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/8b592288208.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/1e59080a4a8.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/3d46534690e.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/e7d2d2dcfa6.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/791e3f3a029.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509095/abffeac0bc1.png</t>
+  </si>
+  <si>
+    <t>DONE ARTICLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># One-Pan Honey Butter Salmon &amp; Rice Recipe
+## Introduction
+One-Pan Honey Butter Salmon &amp; Rice is an exquisite dish that brings together the deliciousness of salmon with a savory-sweet honey glaze and fluffy jasmine rice. This recipe is particularly appealing because it combines flavor, nutrition, and convenience, making it perfect for busy weeknights. The ensemble of ingredients creates a vibrant meal that is quick to prepare and enjoyable to serve, whether you’re hosting family gatherings or just whipping up a cozy dinner for yourself.
+What makes this dish truly unique is its one-pan cooking method, which minimizes cleanup while maximizing flavor. The rich buttery glaze, paired with the delicate salmon and aromatic rice, creates a delightful plate that’s sure to please even the pickiest of eaters. With just a handful of ingredients, you can have a meal that feels gourmet yet is incredibly achievable in your very own kitchen.
+The One-Pan Honey Butter Salmon &amp; Rice is not only visually appealing with its bright colors and textures but also brimming with comforting flavors. It is an excellent choice for a hassle-free lunch or dinner, bringing together freshness and taste in a matter of minutes.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 25 minutes
+- Total Time: 35 minutes
+- Course: Main Course
+- Cuisine: Asian-inspired
+- Servings: 2
+- Calories: ~450 per serving
+## Ingredients
+- 2 salmon fillets
+- 1 cup jasmine rice
+- 2 cups vegetable broth
+- 3 tablespoons honey
+- 2 tablespoons unsalted butter
+- 1 tablespoon soy sauce
+- 2 cloves garlic, minced
+- 1 teaspoon fresh ginger, grated
+- Salt and pepper to taste
+- 2 green onions, sliced (for garnish)
+{{image_ing_1}}
+## Instructions
+1. In a large skillet, melt the butter over medium heat.
+2. Add the minced garlic and grated ginger, sautéing until fragrant, about 1 minute.
+3. Stir in the honey and soy sauce, mixing well to create a glaze.
+4. Push the garlic mixture to the side of the skillet and place the salmon fillets skin-side down in the pan.
+5. Season the salmon with salt and pepper, then cook for 3-4 minutes until slightly browned.
+6. Add the jasmine rice to the skillet, followed by the vegetable broth. Bring to a simmer.
+7. Cover the skillet and reduce the heat to low, cooking for 15-18 minutes or until the rice is tender and the salmon is cooked through.
+8. Remove from heat and let it sit covered for 5 minutes.
+9. Fluff the rice with a fork and drizzle any remaining honey butter glaze over the salmon.
+10. Garnish with sliced green onions before serving.
+### Melting the Butter
+When it comes to melting the unsalted butter for our One-Pan Honey Butter Salmon &amp; Rice, it’s crucial to use the right technique. Unsalted butter is ideal because it allows you to control the salt level in the dish without overwhelming it. Start by placing the butter in a large skillet over medium heat, allowing it to melt evenly. Stir occasionally to prevent browning or burning, as this can alter the flavor profile of your dish. 
+Achieving the right melting technique is vital not only for flavor but also for the subsequent flavors that will be introduced from the garlic and ginger. Ideally, the butter should be melted slowly, with a gentle hiss and sizzle, creating a perfect base for your aromatic ingredients.
+### Sautéing Garlic and Ginger
+Sautéing garlic and ginger in melted butter is the secret to building layers of flavor in One-Pan Honey Butter Salmon &amp; Rice. Once the butter is melted, add the minced garlic and grated ginger and sauté for about a minute, just until you start to smell their aromatic fragrances wafting through your kitchen. Cooking these aromatics at the right temperature and for just the right amount of time is essential—they should soften and turn golden without becoming burnt.
+When garlic and ginger are sautéed correctly, they provide a flavorful foundation. The sweet and spicy notes from the ginger complement the savory garlic, creating an unmatched depth of flavor, which will enhance the overall dish's taste when combined with the salmon and rice.
+### Creating the Honey Soy Glaze
+Now that the garlic and ginger are perfectly cooked, it’s time to create the delicious honey soy glaze that will elevate this dish. To do this, stir in the honey and soy sauce into the skillet with the sautéed mixture. It is important to mix these ingredients well so that they come together seamlessly, forming a glossy glaze that will coat the salmon and rice beautifully.
+To achieve the perfect consistency, take a moment to adjust the quantities to your taste if necessary, but this recipe provides the ideal balance of sweet and savory. The honey will add a sweet richness that pairs beautifully with the salty soy sauce, creating an irresistible glaze that’s simply bursting with flavor.
+## Cooking the Salmon
+### Placing the Salmon in the Skillet
+Once your glaze is ready, carefully push the aromatics to the side of the skillet and place the salmon fillets skin-side down directly into the flavorful mixture. It’s essential to ensure that the fillets are properly spaced apart and fully in contact with the butter and glazes to maximize their flavor development. The skin-side benefits from this direct heat, achieving a crispy texture that contrasts nicely with the tender salmon flesh.
+To gauge when your salmon is ready to flip, keep an eye out for slight browning at the edges—this should take about 3 to 4 minutes. The contrast of textures has never been more delightful than with flaky, perfectly cooked salmon against a cushion of soft rice.
+### Seasoning Techniques
+Properly seasoning the salmon fillets is crucial for enhancing their natural flavor and integrating them with the rest of the dish. Before cooking, sprinkle a generous pinch of salt and freshly cracked pepper on the surface of each fillet. This simple technique enhances the taste of the salmon immensely, allowing the flavors to come alive without overwhelming the dish.
+Salt and pepper not only accentuate the inherent qualities of the salmon but also deepen the flavors of the honey soy glaze. The combination creates a mouthwatering experience that keeps every bite intriguing.
+### Simmering the Rice
+Next, it’s time to add the jasmine rice into the skillet. Pour the rice directly on top of the simmering salmon and glaze. Immediately following the rice, add the vegetable broth, ensuring every grain of rice is saturated in the flavorful liquid. This cooking method allows the rice to soak up the honey-soy flavor while still retaining its own delicate character.
+Bringing the mixture to a simmer is critical—look for small bubbles breaking the surface as the rice begins to absorb the broth. This step is vital for achieving perfectly cooked jasmine rice, which should thread through the dish with its light, fluffy texture.
+## Covering and Cooking
+### Importance of Covering the Skillet
+Covering the skillet is an essential part of the cooking process. This practice not only helps retain heat but creates a steaming effect that ensures the rice cooks evenly and the salmon remains moist and juicy. When the skillet is covered, it creates a mini-oven effect that promotes thorough cooking without the risk of drying out the salmon.
+As you reduce the heat to low, keep in mind that this slow cooking method works wonders, allowing the flavors to meld beautifully and resulting in a truly satisfying meal by the end of the cooking time.
+### Cooking Time and Techniques
+During the ensuing 15 to 18 minutes of cooking, monitor the skillet closely for signs that both the rice and salmon are ready. The salmon should flake easily with a fork, indicating that it's cooked through, while the rice will be tender and absorbent, having soaked in its share of the flavorful broth. These precise cooking times help ensure that you achieve the perfect harmony of flavors and textures necessary for your One-Pan Honey Butter Salmon &amp; Rice.
+By following these steps carefully, you'll be well on your way to creating a dish that's not only satisfying but also packed with flavors that hint at far-off Asian-inspired cuisines, bringing excitement to your dining table.
+## Finishing Touches
+### Resting Period
+After cooking the One-Pan Honey Butter Salmon &amp; Rice, allowing the dish to sit covered for a few minutes is essential. This resting period not only enables the rice to complete its cooking processes but also allows the salmon to absorb the flavorful honey butter glaze fully. By letting the meal rest, you enhance the overall taste as the ingredients meld together, creating a harmonious blend of flavors that accentuate every bite.
+### Fluffing the Rice
+When it’s time to fluff the rice, use a fork rather than a spoon. A fork helps separate the grains without mashing them, which is crucial for maintaining the rice's light and airy texture. Once you’ve pretty much perfected the fluffing technique, you can drizzle any remaining honey butter glaze over the salmon. This addition will amp up the flavor profile, ensuring every component of the dish showcases the tantalizing sweetness of the honey and the richness of the butter.
+### Garnishing with Green Onions
+Green onions play a vital role in enhancing both the visual appeal and flavor of your dish. Their fresh, slightly pungent flavor contrasts beautifully with the sweetness of the honey glaze. For garnishing, slice the green onions thinly; this will allow for even distribution when sprinkled over the finished dish. Ensuring each plate has a generous sprinkle not only heightens the presentation but also enriches the flavor, adding a needed crunch and freshness.
+## Nutritional Benefits
+### Salmon as a Healthful Protein
+Salmon is well-regarded for being one of the healthiest proteins you can consume. Rich in essential nutrients, it offers high-quality protein alongside vitamins and minerals, including B vitamins and selenium. Moreover, salmon is renowned for its omega-3 fatty acids, which are vital for heart health and reducing inflammation. These fatty acids also play a crucial role in brain function, making salmon a valuable component of a balanced diet.
+### Jasmine Rice Benefits
+Jasmine rice, known for its aromatic scent and fluffy texture, is a staple in many Asian cuisines. It has a higher glycemic index compared to other rice types, but it also contains essential nutrients, including carbohydrates for energy and small amounts of protein. In addition to its flavor, jasmine rice offers a lighter option that can complement many dishes without overpowering them, making it a suitable accompaniment to the rich honey butter salmon.
+### Overall Meal Nutrition
+With approximately 450 calories per serving, the One-Pan Honey Butter Salmon &amp; Rice recipe fits well within a healthy meal framework. The whole food ingredients — salmon, jasmine rice, garlic, ginger, honey, and butter — contribute various nutrients that can help create a well-rounded diet. This gentle balance of macronutrients makes it an admirable choice for satisfying hunger while supplying essential nutrients.
+## Variations of the Recipe
+### Alternative Proteins
+If you're considering an alternative to salmon, chicken or tofu can serve as excellent substitutes for this recipe. Chicken breasts will require slightly longer cooking times, about 6-8 minutes on each side, depending on thickness, ensuring they are fully cooked (165°F internal temperature). For tofu, opt for firm or extra-firm tofu, which can be cubed. Simply sauté the cubes until golden brown for that desired texture. Adjust the cooking time accordingly, ensuring the tofu becomes warm and slightly crispy.
+### Substituting Ingredients
+In cases where honey isn’t suitable, alternatives like maple syrup or agave nectar can be utilized instead. Each sweetener will impart its unique flavor, enriching the dish in different but delightful ways. Moreover, for the vegetable broth, feel free to experiment with chicken or mushroom broth to enhance the savory notes of the dish further. The choice of broth will subtly infuse the rice and other ingredients with various flavor undertones.
+## Serving Suggestions
+### Pairing with Vegetables
+This Asian-inspired dish pairs wonderfully with a variety of vegetables that can provide color and nutrition. Steamed broccoli, snap peas, or sautéed spinach are quick options that can be prepared simultaneously while cooking the salmon and rice. Lightly seasoned vegetables offer a vibrant contrast and additional crunch, perfect for rounding out the meal.
+### Wine and Beverage Pairings
+When it comes to beverage pairings, white wines like Sauvignon Blanc or Pinot Grigio complement the honey butter salmon well, enhancing the dish's savory richness. For those seeking non-alcoholic options, consider serving it with a refreshing ginger ale or a mocktail made with sparkling water and lime. Both can enhance the dining experience without overpowering the flavors of the food.
+## Storage and Reheating
+### Storing Leftovers
+Properly storing your One-Pan Honey Butter Salmon &amp; Rice is essential to maintain its flavor and texture. After the dish has cooled, transfer leftovers to an airtight container and keep them in the refrigerator. Properly stored, the meal can last for up to 2-3 days, allowing you to enjoy this delicious dish more than once.
+### Reheating Techniques
+To ensure the salmon and rice retain their flavor and texture, reheating should be done gently. The best method is to place the leftovers in a skillet over low heat, stirring occasionally until warmed through. Alternatively, you can use a microwave, but be mindful to cover the dish to maintain moisture. Avoid reheating the meal multiple times to prevent dry textures.
+## Conclusion
+The One-Pan Honey Butter Salmon &amp; Rice is a perfect combination of sweetness, umami, and comfort, making it an excellent main course choice. The dish's savory glaze and tender salmon contribute to a delightful meal ready in just 35 minutes. With its easy preparation and satisfying flavors, this recipe is bound to become a favorite for busy weeknights.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Juicy Air Fryer BBQ Chicken Bites Recipe
+## Introduction
+The popularity of air fryers has transformed home cooking, allowing for healthier and quicker meal preparation without sacrificing flavor. Among the delightful recipes to emerge from this trend, Juicy Air Fryer BBQ Chicken Bites stand out for their ease of preparation and mouthwatering taste. The air fryer enhances not only the crunchy texture of the chicken bites but also maximizes their juicy goodness, making them an irresistible option for any meal.
+This dish is perfect for a family dinner or as a party appetizer, with its finger food appeal that allows guests to enjoy the delicious BBQ flavor without the need for utensils. With each bite, the juicy chicken is complemented by a tangy and slightly sweet barbecue sauce that brings out its natural flavors. In this article, we will explore how to make this delectable dish, along with tips for achieving the best results.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 12 minutes
+- Total Time: 22 minutes
+- Course: Appetizer/Main Dish
+- Cuisine: American
+- Servings: 4
+- Calories: ~250 per serving
+Juicy Air Fryer BBQ Chicken Bites offer a savory and sweet flavor profile that's hard to resist. With a preparation time of just 10 minutes and a cook time of 12 minutes, this dish is perfect for those busy weeknights when time is of the essence. The combination of juicy chicken and tangy barbecue sauce makes this recipe a crowd favorite.
+## Ingredients
+To create these delicious BBQ chicken bites, you will need the following ingredients:
+- 1 pound chicken breast, cut into bite-sized pieces
+- 1 cup barbecue sauce
+- 1 tablespoon olive oil
+- 1 teaspoon garlic powder
+- 1 teaspoon onion powder
+- Salt and pepper to taste
+- Fresh parsley for garnish (optional)
+{{image_ing_1}}
+## Instructions
+1. In a mixing bowl, combine the chicken pieces with olive oil, garlic powder, onion powder, salt, and pepper. Toss until the chicken is evenly coated.
+2. Add the barbecue sauce to the chicken and mix until all pieces are well coated.
+3. Preheat the air fryer to 400°F (200°C) for about 5 minutes.
+4. Place the sauced chicken bites in a single layer in the air fryer basket, making sure they are not overcrowded.
+5. Cook the chicken bites in the air fryer for 10-12 minutes, shaking the basket halfway through to ensure even cooking.
+6. Check the internal temperature of the chicken; it should reach 165°F (75°C).
+7. Once cooked, remove the chicken bites from the air fryer and let them rest for a few minutes.
+8. Garnish with fresh parsley if desired and serve with extra barbecue sauce on the side.
+## Cooking Equipment
+To successfully prepare Juicy Air Fryer BBQ Chicken Bites, you will need the following cooking equipment:
+- Air fryer: The essential tool for achieving that crispiness without deep frying.
+- Mixing bowl: For combining the chicken with the oils and seasonings.
+- Measuring spoons: Necessary for accurate measurements of the spices and oil used in the recipe.
+- Meat thermometer: A handy tool to ensure that the chicken has reached a safe internal temperature before serving.
+- Serving platter: To present your delicious chicken bites beautifully to guests or family.
+## Preparation Steps
+### Chicken Preparation
+Before diving into the cooking process, start by preparing the chicken. Begin by cutting the chicken breast into bite-sized pieces to ensure even cooking. Uniformity in size helps the pieces to cook at the same rate, providing a consistent texture throughout. Patting the chicken dry with a paper towel is an important step, as it helps the seasoning adhere better to the meat, giving each bite a robust flavor.
+### Seasoning the Chicken
+In a mixing bowl, combine the chicken pieces with olive oil, garlic powder, onion powder, salt, and pepper. By using olive oil, you'll not only add flavor but also help create a delightful crispness when the chicken is air-fried. Toss the chicken until evenly coated to maximize the flavor infusion. Ensuring that every piece is seasoned well contributes to the overall taste of the finished product.
+### Saucing the Chicken
+Once the chicken is seasoned, it's time to make it BBQ-ready. Add the barbecue sauce to the seasoned chicken. The sauce is the star of this dish; it not only adds flavor but also contributes to the shiny glaze that makes these chicken bites appealing. Mix thoroughly to ensure that each piece is well coated in the sauce. This step is crucial for achieving that deliciously sticky texture that BBQ lovers crave.
+## Air Frying Techniques
+### Preheating the Air Fryer
+Preheating the air fryer to 400°F (200°C) for approximately 5 minutes is a crucial step in this cooking method. This ensures the chicken cooks evenly from the start, leading to a perfect golden-brown finish. An air fryer that hasn't been preheated will not reach the desired temperature quickly enough, potentially resulting in uneven cooking.
+### Cooking the Chicken Bites
+After preheating, it's time to cook the chicken bites. Place the sauced chicken bites in a single layer in the air fryer basket, avoiding overcrowding to promote even cooking. Air fryers rely on hot air circulation to cook the food, and crowding the basket can hinder this movement, resulting in soggy bites instead of that desired crispiness. Once placed in the basket, the chicken bits will be ready to turn into delicious, juicy morsels that are hard to resist.
+### Timing and Cooking Tips
+Cooking chicken bites to perfection requires careful timing and attention to detail. The recommended cooking duration for the juicy air fryer BBQ chicken bites is between 10 to 12 minutes. For optimal results, it’s essential to shake the basket halfway through the cooking process. This technique ensures that each piece cooks evenly and achieves a delicious, caramelized exterior. 
+Moreover, monitoring the internal temperature of the chicken is crucial for ensuring the safety of your meal. The USDA recommends that chicken be cooked to an internal temperature of 165°F (75°C) to eliminate harmful bacteria. A quick check with a meat thermometer not only guarantees food safety but also helps retain the juiciness of the chicken, making each bite tender and flavorful.
+## Checking for Doneness
+### Importance of Temperature
+Using a meat thermometer is essential when cooking chicken, especially when air frying. This tool allows you to verify that the chicken is thoroughly cooked. Proper cooking temperature is key to preventing any foodborne illnesses while also ensuring that the meat is deliciously juicy. As the chicken bites reach the required internal temperature of 165°F (75°C), you’ll notice they are not only safe to consume but also retain their rich flavors and tender textures.
+### Visual Cues
+In addition to checking the internal temperature, visual cues can further confirm that your chicken bites are done. A nicely caramelized exterior is an excellent indicator of flavor development, showing that the sugars in the barbecue sauce have cooked to create that sought-after glaze. Inside, the chicken should no longer be pink, and the texture will reveal a moist and tender piece of meat. After cooking, allowing the chicken to rest for a few minutes can significantly enhance juiciness as it holds onto its natural moisture.
+## Serving Suggestions
+### Presentation Ideas
+Presentation can elevate your dish from good to great. When serving the juicy air fryer BBQ chicken bites, consider arranging them on a large serving platter to create an inviting display for your guests. To add a visually appealing touch, sprinkle freshly chopped parsley over the top. This not only enhances the aesthetics but also offers a fresh flavor contrast to the rich barbecue sauce.
+### Accompanying Sauces
+While the chicken bites are scrumptiously coated in barbecue sauce, serving additional dipping sauces on the side can enhance the flavor experience. A bowl of extra barbecue sauce allows guests to customize their bites to their taste. For those looking to vary their flavor palette, pairing with ranch dressing or blue cheese dressing can introduce some delightful tanginess that complements the smoky roasted notes of the chicken.
+## Nutritional Information
+### Caloric and Nutritional Breakdown
+Understanding the nutritional profile of your dish is essential, especially for those mindful of their dietary intake. Each serving of the juicy air fryer BBQ chicken bites contains approximately 250 calories, making it a relatively light yet flavorful option. This dish is appropriately versatile for both appetizers at gatherings and as a satisfying main course for family dinners. With a balance of protein from chicken and the robust flavor of barbecue sauce, it serves as an enticing meal choice that does not compromise on taste.
+## Variations and Substitutions
+### Alternative Proteins
+If you’re looking to accommodate different dietary preferences or simply wish to try something new, consider substituting chicken with alternative proteins. Turkey breast can be an excellent lean option that cooks similarly, while tofu provides a vegetarian alternative that can absorb flavors wonderfully. Just keep in mind that cooking times may vary slightly based on the type of protein used.
+### Flavor Enhancements
+Experimenting with flavors is one of the joys of cooking. To change up the flavor profile of your chicken bites, think about using different varieties of barbecue sauce. From sweet and tangy to spicy and smoky, the possibilities are nearly endless. Additionally, consider enhancing the flavor with spices like smoked paprika or a pinch of cayenne pepper for a bit of heat. These simple adjustments can bring new life to the recipe and make it uniquely your own.
+## Storing Leftovers
+### Proper Storage Techniques
+To keep your juicy air fryer BBQ chicken bites fresh for future enjoyment, proper storage techniques are vital. Begin by allowing any leftovers to cool completely. Once they’ve reached room temperature, store them in an airtight container in the refrigerator. This prevents moisture build-up, which can affect the overall texture and flavor of the chicken bites.
+### Reheating Instructions
+When you’re ready to enjoy the leftovers, reheating them correctly is essential to restore their original charm. Placing the chicken bites back into the air fryer for 3 to 5 minutes will effectively crispen them up, mimicking the texture achieved during the initial cooking. Alternatively, you can use the microwave for a quicker reheat, but be aware that this method may lead to softer texture due to moisture accumulation.
+## Conclusion
+Juicy Air Fryer BBQ Chicken Bites combine flavor and convenience, making them a fantastic choice for any occasion. The brief prep and cook time ensure they fit seamlessly into busy lifestyles while still delivering a satisfying culinary experience. The combination of well-seasoned chicken and rich barbecue sauce offers a delightful treat that is enjoyable both as an appetizer and a main dish, appealing to a wide range of taste preferences.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Healthy Greek Chicken Bowls Recipe
+## Introduction
+Exploring the vibrant flavors of Greek cuisine, this article delves into the delicious and nutritious Healthy Greek Chicken Bowls. Perfect for a wholesome meal, these bowls combine seasoned chicken with fresh vegetables and protein-rich quinoa, making it a balanced main course. Beyond mere nutrition, these bowls are a celebration of color, texture, and taste, reminiscent of sunny Mediterranean days. 
+Whether you are looking to whip up a quick dinner during a busy week or meal prep for the days ahead, the Healthy Greek Chicken Bowls provide a nourishing option that is just as satisfying as it is wholesome. The blend of rich ingredients offers an engaging culinary experience that will make your taste buds dance, ensuring that this recipe can become a staple in your household.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 25 minutes
+- Total Time: 40 minutes
+- Course: Main Course
+- Cuisine: Greek
+- Servings: 4
+- Calories: ~450 per serving
+Healthy Greek Chicken Bowls are a delightful representation of Greek flavors, featuring tender chicken, fresh veggies, and creamy feta. This dish is perfect for meal prep or family dinners, promising satisfaction that aligns with healthy eating.
+## Ingredients
+- 2 boneless, skinless chicken breasts
+- 1 cup quinoa, rinsed
+- 1 tablespoon olive oil
+- 1 teaspoon dried oregano
+- 1 teaspoon garlic powder
+- Salt and pepper to taste
+- 1 cup cherry tomatoes, halved
+- 1 cucumber, diced
+- 1/2 red onion, thinly sliced
+- 1/2 cup feta cheese, crumbled
+- 1/4 cup Kalamata olives, pitted and halved
+- Fresh parsley for garnish
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 400°F (200°C).
+2. In a small bowl, mix olive oil, oregano, garlic powder, salt, and pepper. Rub this mixture onto the chicken breasts.
+3. Place the seasoned chicken on a baking sheet and bake for 20-25 minutes, or until cooked through and juices run clear.
+4. While the chicken is baking, cook the quinoa according to package instructions. Fluff with a fork once done.
+5. In a large bowl, combine cherry tomatoes, cucumber, red onion, feta cheese, and Kalamata olives. Toss gently to mix.
+6. Once the chicken is cooked, let it rest for a few minutes, then slice it into strips.
+7. To assemble the bowls, start with a base of quinoa, top with the veggie mixture, and add sliced chicken on top.
+8. Garnish with fresh parsley before serving.
+## Health Benefits
+### Nutritional Value of Chicken
+Chicken is often considered a lean source of protein and is frequently included in healthy diets. Notably, boneless, skinless chicken breasts provide a protein boost while containing significantly less fat compared to other cuts. With approximately 26 grams of protein per 3-ounce serving, chicken is excellent for muscle repair and growth. It also contains essential nutrients such as niacin, vitamin B6, and selenium, contributing to overall health and wellbeing. By incorporating chicken into your Healthy Greek Chicken Bowls, you not only enhance the flavor but also provide your body with necessary nutrients that promote good health.
+### Advantages of Quinoa
+Quinoa, often heralded as a superfood, is a game changer in this recipe. Unlike many grains, quinoa is a complete protein, meaning it contains all nine essential amino acids needed by the body. This characteristic makes it an ideal choice for vegetarians, but even meat lovers can appreciate its nutritional benefits. Quinoa is also gluten-free, making it suitable for those with dietary restrictions. With its high fiber content, it helps in maintaining a healthy digestive system and provides lasting energy. Additionally, quinoa is rich in minerals such as magnesium, iron, and phosphorus, contributing further to its status as a nutritional powerhouse.
+### Fresh Vegetables and Their Benefits
+The combination of fresh vegetables in the Healthy Greek Chicken Bowls not only adds vibrancy and crunch but also elevates the dish's nutritional profile. Cherry tomatoes are low in calories but high in vitamins A and C, both of which are potent antioxidants. The cucumber provides hydration and contains anti-inflammatory properties, making it refreshing and beneficial for overall health. Red onions contribute antioxidants that may support heart health while also lowering cholesterol levels. The inclusion of Kalamata olives introduces healthy fats, specifically monounsaturated fat, which is known to promote cardiovascular health. Together, the fresh produce enhances not just the flavor but also the fiber content, aiding digestion and contributing to a well-balanced meal.
+## Cooking Techniques
+### Baking Chicken
+Baking chicken is an excellent method that locks in moisture, providing a tender and juicy finish without excessive oil. Preheating the oven to 400°F (200°C) ensures that the chicken cooks evenly. Applying the olive oil and spice rub before baking enhances the flavor while forming a slight crust. Baking time is crucial; the chicken should reach an internal temperature of 165°F (74°C) to ensure that it is fully cooked. Allowing the chicken to rest after baking is equally important, as this step allows the juices to redistribute, yielding perfectly sliced chicken that remains succulent.
+### Cooking Quinoa Perfectly
+Cooking quinoa to perfection requires attention to detail, as it can easily become mushy if overcooked. The basic rule of thumb is to use a 2:1 water-to-quinoa ratio. Rinsing the quinoa before cooking helps remove the saponin coating, which can impart a bitter taste. Simmering on low heat allows the grains to absorb moisture while releasing their natural flavors. Once cooked, fluffing the quinoa with a fork instead of stirring with a spoon maintains the integrity of each grain, resulting in a light and fluffy base for your bowl.
+### Tossing Vegetables
+When preparing the fresh vegetable mix, gentle tossing is essential to keep the ingredients’ freshness and crunch intact. Chopping the vegetables uniformly ensures that they combine well in each bite, offering a delightful contrast to the tender chicken and quinoa. 
+Taking care not to bruise the ingredients while mixing will maintain their vibrant colors and crisp textures. Using the right bowl size is also essential; a large bowl provides ample room for mixing without squishing the vegetables, preserving their individual flavors and providing a visually appealing presentation in the Healthy Greek Chicken Bowls.
+### Preparing the Chicken
+The foundation of your Healthy Greek Chicken Bowls begins with perfectly seasoned and baked chicken breasts. Start by preheating your oven to 400°F (200°C). While the oven warms up, take your two boneless, skinless chicken breasts and dry them with paper towels to ensure a good sear and flavor absorption. In a small bowl, combine 1 tablespoon of olive oil, 1 teaspoon of dried oregano, and 1 teaspoon of garlic powder, and season with salt and pepper to taste.
+Once this mixture is ready, rub it generously over each chicken breast, ensuring that the flavors penetrate into the meat. This step not only enhances the taste but also contributes to a delicious crust when baked. After seasoning, place the chicken breasts on a lined baking sheet. Bake for 20 to 25 minutes, or until the chicken is thoroughly cooked and the juices run clear. This method helps lock in moisture, leaving you with succulent, flavorful chicken.
+### Cooking the Quinoa
+While the chicken is baking, it’s essential to focus on cooking the quinoa correctly to achieve its fluffy texture and nutty flavor. Gather 1 cup of rinsed quinoa, which helps remove any bitterness from the seeds. Cook the quinoa according to the package instructions—typically by using a 2:1 ratio of water to quinoa. Bring the water to a rolling boil, add the quinoa, reduce the heat to low, cover, and simmer for about 15 minutes until the water is absorbed.
+Once cooked, take the quinoa off the heat and let it sit covered for an additional 5 minutes. This allows any remaining steam to finish cooking the grains. Fluff the quinoa with a fork afterward, separating the grains to give it an airy texture. This light and fluffy quinoa will serve as the perfect base for your Greek chicken bowls, absorbing flavors from the other ingredients beautifully.
+### Assembling the Bowl
+The art of assembling your Healthy Greek Chicken Bowls lies in layering the ingredients to create an aesthetically pleasing dish. Start with a generous scoop of the fluffed quinoa at the bottom of each serving bowl. This serves as the hearty base of the meal, rich in protein and fiber.
+Next, take your fresh vegetable mixture, which should consist of halved cherry tomatoes, diced cucumber, thinly sliced red onion, and Kalamata olives. Disperse this vibrant blend over the quinoa, allowing the colors to shine through and enhance the visual appeal. The Mediterranean medley is not only nutritious but also adds a refreshing crunch to the bowl.
+Finally, slice the baked chicken breasts into strips and layer them on top of the salad mixture. This presentation not only keeps the chicken moist but also allows diners to see the beautiful golden-brown exterior. For a final touch of elegance and flavor, sprinkle ½ cup of crumbled feta cheese and garnish with fresh parsley. These visual elements tantalize the taste buds even before the first bite.
+## Flavor Combinations
+### The Role of Feta
+Feta cheese plays a critical role in the flavor profile of your Healthy Greek Chicken Bowls. Its tangy, creamy texture provides a delicious contrast to the savory chicken and the freshness of the vegetables. The crumbly nature of feta allows it to blend beautifully into each bowl, enhancing the overall taste. Moreover, feta is known for its low-fat content compared to many other cheese varieties, making it a healthier choice without sacrificing flavor.
+### Harmonizing Herbs and Spices
+The seasoning mix of dried oregano and garlic powder not only enhances the chicken but also complements the whole dish. Oregano brings a warm, earthy quality that is characteristic of Greek cuisine, while garlic powder adds a depth of flavor without overpowering the other ingredients. The harmony of these herbs and spices creates a mouthwatering experience that will have everyone asking for seconds.
+### The Crunch of Fresh Vegetables
+Incorporating fresh vegetables like cucumbers and cherry tomatoes not only adds layers of flavor but also enhances the texture of your dish. Crisp cucumbers provide a refreshing crunch, which contrasts nicely with the tender chicken and fluffy quinoa. Cherry tomatoes burst with juiciness, bringing an element of sweetness to the mix. Together, these vegetables contribute essential vitamins and minerals, making your meals not just delicious but also nutritious.
+## Preparation and Timing
+### Prep Time Breakdown
+To maximize efficiency during the preparation process, consider organizing your cooking steps. Start by preheating the oven and preparing the chicken. While the chicken is marinating with the seasoning, rinse the quinoa and chop your vegetables. This multitasking approach takes full advantage of the 15 minutes allocated for prep time, ensuring that everything is ready when you need it.
+### Cooking Timeline
+The total cooking time for this meal is just 40 minutes, allowing you to put together a wholesome dinner without spending excessive time in the kitchen. After placing the chicken in the oven, use the 25 minutes it cooks to focus on the quinoa and vegetable preparation. By the time the chicken is done resting, your quinoa will be fluffy and the vegetable mixture will be ready, making for a smooth assembly process.
+## Serving Suggestions
+### Ideal Pairings
+To elevate your Healthy Greek Chicken Bowls even further, consider pairing them with a side of pita bread or a light tzatziki sauce. The warm, pillowy pita can be used to scoop up the quinoa and chicken, enhancing the Mediterranean experience. A drizzle of tzatziki adds a cool, creamy contrast that ties the dish together beautifully. 
+### Meal Prep Options
+If you're looking to create a meal prep version of this dish, consider preparing the chicken, quinoa, and vegetables in advance. Store each component separately in airtight containers in the refrigerator to ensure freshness. When you're ready to enjoy, simply reheat the chicken and quinoa and assemble your bowl, making nutritious eating convenient.
+### Presentation Tips
+When serving your Healthy Greek Chicken Bowls to guests or family, consider using clear bowls to showcase the vibrant layers of color. Additionally, an extra sprinkle of feta and chopped parsley right before serving adds a fresh touch. Finally, consider drizzling a little extra olive oil or balsamic reduction over the top for added flavor complexity.
+## Ingredient Substitutions
+### Alternative Proteins
+If chicken isn't your preferred protein or you’re looking for a different option, consider using grilled shrimp or tofu. Both options will absorb the same seasonings beautifully and can be cooked similarly. Choose a firm tofu to provide a satisfying texture and grilling marks that resemble delicious chicken.
+### Gluten-Free Options
+This recipe can easily be adapted for gluten-free diets by ensuring that the quinoa you choose is certified gluten-free. Most quinoa varieties naturally fit this requirement, making it a perfect choice for anyone avoiding gluten while still enjoying a hearty meal. 
+### Dairy Alternatives
+For those with lactose intolerance or a dairy-free preference, consider using a plant-based cheese alternative. Nutritional yeast can also replicate some of the cheesy flavor and nutty profile that feta provides, ensuring your bowls are still delicious without dairy.
+## Conclusion
+The Healthy Greek Chicken Bowls are a vibrant dish filled with robust flavors and textures. The combination of tender chicken, nutritious quinoa, and fresh vegetables results in a satisfying and healthful meal that can be prepared in under 40 minutes. Enjoy the blend of Mediterranean tastes as you savor every bite.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Soft &amp; Fluffy Homemade Cinnamon Rolls Recipe
+## Introduction
+Cinnamon rolls are a beloved classic in American cuisine, combining fluffy dough with a rich filling of cinnamon and sugar. They serve as a delightful breakfast treat or dessert that can warm your heart and home. The unmistakable aroma wafting through the kitchen during baking captivates attention and ignites nostalgia for many. This recipe for Soft &amp; Fluffy Homemade Cinnamon Rolls promises to deliver that perfect blend of taste and texture, ensuring that each roll is a moment of indulgence.
+Picture a Saturday morning with the family gathered around the table, or perhaps a holiday breakfast where everyone anticipates the sweet surprise that awaits. These cinnamon rolls are not just a dish; they embody the very essence of comfort food. Soft, airy, and filled with a gooey brown sugar and cinnamon mixture, each roll is a revelation of flavors. Topped with a luscious cream cheese icing, they become decadent treats that everyone will love.
+This recipe is straightforward enough for novice bakers yet rewarding for experienced cooks who relish the process of homemade baking. Whether served freshly baked at brunch or warmed up later in the week, these cinnamon rolls remain a delightful indulgence. 
+## Recipe Overview
+- Prep Time: 30 minutes
+- Cook Time: 25 minutes
+- Total Time: 1 hour 55 minutes
+- Course: Breakfast/Dessert
+- Cuisine: American
+- Servings: 12
+- Calories: ~250 per roll
+This homemade cinnamon roll recipe offers a step-by-step guide to creating soft, fluffy rolls filled with cinnamon and brown sugar goodness. Perfect for sharing or enjoying on your own, these rolls are ideal for breakfast, brunch, or dessert. With a total preparation and cooking time of just under two hours, you can easily impress your family and friends.
+### Flavor Profile
+Rich flavors of cinnamon and brown sugar harmonize beautifully with a creamy icing, offering a sweet balance that pleases every palate. The dough is light and airy, while the filling is a warm hug of sweetness that complements the rolls' soft texture. Adding the cream cheese icing elevates each bite, adding a luxurious finish that rounds out the overall flavor experience. 
+### Ideal Occasions
+These cinnamon rolls are perfect for a variety of occasions, including holiday breakfasts, weekend brunches, or simply for satisfying sweet cravings any day of the week. They could even become the centerpiece of your next family gathering. With their inviting aroma and delectable flavor, these rolls have an innate ability to bring people together.
+### Storage Suggestions
+If you have any leftovers, learn how to store and reheat these rolls to enjoy their delightful flavor even days later. Properly storing the cinnamon rolls is key to preserving their soft texture. They can be wrapped in plastic wrap and kept in the refrigerator for up to a few days. To enjoy them warm again, simply pop them into the oven for a few minutes or microwave them for a few seconds—just enough to take the chill off without compromising their fluffiness.
+## Ingredients
+### To make these Soft &amp; Fluffy Homemade Cinnamon Rolls, gather the following ingredients:
+### Dry Ingredients
+- All-purpose flour
+- Granulated sugar
+- Salt
+- Ground cinnamon
+### Wet Ingredients
+- Warm milk (110°F)
+- Unsalted butter, melted
+- Large eggs
+- Active dry yeast
+### Filling Components
+- Brown sugar
+- Ground cinnamon
+### Icing Ingredients
+- Cream cheese, softened
+- Powdered sugar
+- Additional milk
+{{image_ing_1}}
+## Instructions
+1. In a small bowl, combine warm milk and yeast. Let sit for 5-10 minutes until frothy.
+2. In a large mixing bowl, whisk together flour, sugar, and salt.
+3. Add the melted butter, eggs, and the yeast mixture to the dry ingredients. Mix until a dough forms.
+4. Knead the dough on a floured surface for about 5-7 minutes until smooth and elastic.
+5. Place the dough in a greased bowl, cover with a cloth, and let it rise in a warm place for 1 hour or until doubled in size.
+6. Once risen, roll out the dough into a rectangle about 1/4 inch thick.
+7. Spread softened butter over the dough, then sprinkle with brown sugar and cinnamon.
+8. Roll the dough tightly from the long side and cut into 12 equal pieces.
+9. Place the rolls in a greased baking dish and let them rise for another 30 minutes.
+10. Preheat the oven to 350°F (175°C) and bake the rolls for 20-25 minutes until golden brown.
+11. While the rolls are baking, mix cream cheese, powdered sugar, and milk to create the icing. Drizzle over warm rolls before serving.
+Getting these steps right is essential for achieving the softest, fluffed rolls. 
+## Preparing the Dough
+Understanding the dough preparation process ensures optimal results for your cinnamon rolls. The first step in making these cinnamon rolls is to activate the yeast, which is crucial in achieving that light and airy structure. 
+### Activating the Yeast
+Learn how to properly activate the yeast with warm milk and what signs indicate that it's ready to use. Using milk at the right temperature is essential; it should be warm but not scalding hot. When the yeast is added to the warm milk, you should observe it frothing within a few minutes. This foam is a positive sign that the yeast is alive and well, ready to help your dough rise.
+### Mixing the Ingredients
+Discover the correct method for combining dry and wet ingredients to achieve a uniform dough mixture. It’s essential to blend the flour, sugar, and salt first to ensure even distribution before introducing the wet ingredients. Once your butter, eggs, and yeast mixture are poured in, mix adequately until a rough dough forms. This is the foundation of your beloved cinnamon rolls.
+### Kneading the Dough
+Explore the techniques for kneading dough effectively to develop gluten, ensuring the rolls are fluffy. Kneading transforms the dough into a cohesive ball and aids in gluten development. A well-kneaded dough should be smooth, elastic, and slightly tacky to the touch. The joy of fresh baking starts here, where your hands work the ingredients into a beautiful dough ready to rise and shine. 
+## First Rise
+The initial rise of the dough is crucial to developing flavor and texture. During this time, the yeast ferments, producing gas that causes the dough to expand. This step not only affects the final texture of the cinnamon rolls but also adds depth to their flavor. 
+### Preparing the Rising Environment
+For optimal results, place the covered dough in a warm, draft-free environment. The warmth will encourage the yeast to work its magic. If your kitchen is cool, you can turn on your oven for a minute to slightly warm it up or place the bowl in a sunny spot. It usually takes about an hour for the dough to double in size, but this can vary based on the room temperature and yeast activity.
+As you follow each step to create these delightful cinnamon rolls, keep an eye on the texture and smell of the dough. The anticipation builds as you see it rise, paving the way for the next steps in this baking adventure. Stay tuned for more on the rolling, filling, and the blissfully aromatic baking process in the next part of this recipe journey.
+### Creating a Warm Area for Dough to Rise
+When it comes to allowing your homemade cinnamon roll dough to rise, the environment plays a key role in the fermentation process. A warm and draft-free area can significantly increase the speed of dough rising. Here are some effective methods to create the perfect rising environment:
+- **Oven Method**: Preheat your oven to the lowest setting, about 150°F (65°C), and then turn it off. Place the dough inside, leaving the oven door ajar. The residual heat creates a warm atmosphere that encourages the yeast to activate quickly.
+- **Microwave Trick**: Another great technique is to use your microwave. Boil a cup of water and place it in the microwave along with the bowl of dough. The steam from the water helps create a warm, moist environment that is ideal for rising.
+- **Warm Surface**: Alternatively, place the dough on a countertop warmed by exposure to sunlight or near a heater. This natural warmth can also help in speeding up the rise.
+### Time Requirements
+After techniques for creating the perfect environment have been established, it’s essential to understand the timing for each stage of the rising process. The first rise generally takes about **1 hour**, during which you should look for visual cues. The dough should double in size and become puffy and airy. 
+After rolling and cutting the dough, the second rise lasts for approximately **30 minutes**, leading to even fluffier cinnamon rolls. During this period, the dough will expand, filling the gaps between rolls, which increases the overall texture and taste.
+## Rolling Out the Dough
+Rolling out your dough correctly is a vital step in assembling your cinnamon rolls. This will determine the thickness and the overall appearance of each roll.
+### Tools and Techniques
+To effectively roll out your dough, consider using the following tools and techniques:
+- **Rolling Pin**: A good quality wooden or silicone rolling pin ensures even distribution of pressure as you roll the dough out.
+- **Floured Surface**: Dust your working surface with flour to prevent sticking. Too much flour can lead to dry rolls, so moderate your use appropriately.
+- **Guided Measurements**: Aim for a rectangle approximately 1/4 inch thick. Using a ruler can help you maintain uniformity.
+By keeping these tips in mind, you will be able to achieve an even thickness, which results in consistent baking.
+### Creating the Filling
+The filling for your cinnamon rolls is what makes them truly irresistible. Here’s how to prepare it effectively:
+1. **Melted Butter**: Start by melting your butter and ensuring it is cool before spreading it on the dough. It's important as hot butter can overly soften the dough, making it difficult to work with.
+2. **Sugar and Cinnamon**: In a separate bowl, mix together your granulated brown sugar and ground cinnamon. This will make it easier when you sprinkle the mixture on the butter-covered dough.
+Ensure even coverage when applying both melted butter and the sugar-cinnamon mixture for maximum flavor distribution. 
+## Shaping the Rolls
+The appearance and texture of your cinnamon rolls depend greatly on how you shape them.
+### Rolling the Dough
+### To achieve that iconic cinnamon swirl, follow these steps:
+- Begin rolling from the long edge of the rectangle. This will create wider rolls, which are typically easier to cut and have a grander appearance.
+- Apply equal pressure while rolling to ensure a tight roll. A loose roll can cause the cinnamon filling to leak out while baking, leading to uneven cooking.
+### Cutting the Rolls
+Once you’ve rolled the dough into a log, it’s time to cut:
+- **Sharp Knife or Dental Floss**: Use a sharp knife or unflavored dental floss for clean cuts. This ensures that you don't squish the dough and retain its structure. To use floss, slide it under the roll and cross it at the top, pulling to cut gently.
+- **Equal Slices**: Aim for 12 equal pieces so they cook uniformly. Uniformity ensures that all rolls are baked for the same amount of time, yielding perfectly cooked treats.
+## Second Rise
+Allowing your shaped rolls to rise again is crucial to achieve the desired airy texture.
+### Duration of Second Rise
+After cutting the rolls, let them rest and rise for an additional **30 minutes**. During this time, you should notice an increase in volume, which indicates that the yeast is actively working. Look for the rolls to expand significantly; they should not spring back when gently pressed.
+### Greasiness and Placement
+To secure that your cinnamon rolls are perfectly baked and easy to serve, pay attention to your greasing method:
+- **Greased Baking Dish**: Use non-stick spray or a thin layer of butter to coat the bottom and sides of your baking dish. This prevents them from sticking and helps achieve a beautiful golden brown coloring.
+- **Spaced Placement**: Arrange your rolls with enough space between them to allow for expansion during the second rise. This prevents them from merging together and ensures optimal air circulation while baking.
+## Baking the Cinnamon Rolls
+As the time nears to bake your rolls, focus on these final steps.
+### Oven Temperature
+Preheating your oven to **350°F (175°C)** is essential as it ensures that the rolls will bake evenly from the moment they go in. An oven thermometer can help you verify that your temperature is accurate, preventing over-baking or under-baking.
+### Baking Time
+Bake the rolls in your preheated oven for **20-25 minutes**. It’s important to keep an eye on them; you’re looking for a beautiful golden-brown color. They should be soft to the touch, and a toothpick inserted in the center should come out clean.
+## Making the Icing
+The icing adds the final flourish to your cinnamon rolls, making them even more delectable.
+### Ingredients for Icing
+To create a rich and creamy icing, you’ll need the following ingredients:
+- Cream cheese
+- Powdered sugar
+- Milk
+These elements combine to create a smooth consistency perfect for drizzling over the warm rolls.
+### Mixing the Icing
+### Follow these steps for preparing the icing:
+1. In a bowl, mix softened cream cheese, powdered sugar, and milk. 
+2. Use an electric mixer or a whisk to combine until smooth. Aim for a consistency that is thick enough to hold its shape but thin enough to drizzle easily.
+## Serving Suggestions
+Enhance the experience of your homemade cinnamon rolls with these serving suggestions.
+### Pairing with Beverages
+Cinnamon rolls pair beautifully with a variety of beverages. Consider serving them with a rich cup of coffee or a glass of fresh milk. They also complement herbal teas very well, offering a balance between sweetness and warmth.
+### Garnishing Options
+A sprinkle of extra cinnamon or a dash of finely grated orange zest can provide a lovely visual touch and aromatic appeal. You could also consider garnishing with chopped nuts or coconut flakes for added texture.
+## Conclusion
+Soft &amp; Fluffy Homemade Cinnamon Rolls are an inviting breakfast or dessert option, with delightful sweetness and a tender texture that’s hard to resist. The preparation time is manageable, making this a suitable recipe for any occasion for families or social gatherings. Each roll is approximately 250 calories, making it a pleasurable yet indulgent treat.
+</t>
+  </si>
+  <si>
+    <t>One-Pan Honey Butter Salmon &amp; Rice Recipe</t>
+  </si>
+  <si>
+    <t>Juicy Air Fryer BBQ Chicken Bites Recipe</t>
+  </si>
+  <si>
+    <t>Healthy Greek Chicken Bowls Recipe</t>
+  </si>
+  <si>
+    <t>Soft &amp; Fluffy Homemade Cinnamon Rolls Recipe</t>
+  </si>
+  <si>
+    <t>Easy One-Pan Honey Butter Salmon with Jasmine Rice Recipe</t>
+  </si>
+  <si>
+    <t>Easy Air Fryer BBQ Chicken Bites Recipe for Quick and Juicy Appetizers</t>
+  </si>
+  <si>
+    <t>Healthy Greek Chicken Bowls with Quinoa and Feta for a Delicious Meal</t>
+  </si>
+  <si>
+    <t>Soft and Fluffy Homemade Cinnamon Rolls Recipe for Breakfast or Dessert</t>
+  </si>
+  <si>
+    <t>Honey Butter Salmon with Jasmine Rice</t>
+  </si>
+  <si>
+    <t>Savory Air Fryer BBQ Chicken Bites</t>
+  </si>
+  <si>
+    <t>Mediterranean Chicken Quinoa Bowls</t>
+  </si>
+  <si>
+    <t>Fluffy Homemade Cinnamon Roll Delight</t>
+  </si>
+  <si>
+    <t>Discover the joy of cooking with this easy one-pan honey butter salmon recipe paired with fragrant jasmine rice. This quick recipe offers a delightful Asian-inspired twist that's perfect for a weeknight dinner or a cozy weekend meal. Enjoy the rich flavors and minimal cleanup while savoring a dish that brings warmth to your table.</t>
+  </si>
+  <si>
+    <t>Discover the joy of easy cooking with this Air Fryer BBQ Chicken Bites recipe, perfect for quick and juicy appetizers any time of the year. These flavorful bites make an ideal addition to your dinner table or game day spread, allowing you to whip up a delicious meal in no time. Enjoy the smoky BBQ flavor combined with the convenience of an air fryer for an effortless dish that everyone will love.</t>
+  </si>
+  <si>
+    <t>Enjoy a vibrant and nourishing meal with these Healthy Greek Chicken Bowls featuring quinoa and feta cheese. This Mediterranean diet-inspired recipe is perfect for meal prep, offering a delicious blend of fresh flavors and wholesome ingredients. Elevate your lunch or dinner routine with a satisfying quinoa salad that will delight your taste buds and nourish your body.</t>
+  </si>
+  <si>
+    <t>Indulge in the comforting warmth of homemade cinnamon rolls, perfect for breakfast or dessert. This soft and fluffy recipe is easy to make and topped with a luscious icing that will delight your taste buds. Treat yourself and your loved ones to this sweet classic that fills your home with the inviting aroma of cinnamon.</t>
+  </si>
+  <si>
+    <t>salmon, honey butter, one-pan, jasmine rice, quick recipe, Asian-inspired</t>
+  </si>
+  <si>
+    <t>Air Fryer, BBQ Chicken, Recipe, Quick Meal, Easy Dinner, Appetizer</t>
+  </si>
+  <si>
+    <t>Greek chicken bowls, healthy recipe, quinoa salad, feta cheese, Mediterranean diet, meal prep</t>
+  </si>
+  <si>
+    <t>cinnamon rolls, homemade, fluffy, breakfast, dessert, icing</t>
+  </si>
+  <si>
+    <t>Honey Butter Salmon Rice</t>
+  </si>
+  <si>
+    <t>Air Fryer BBQ Chicken Bites</t>
+  </si>
+  <si>
+    <t>Homemade Cinnamon Rolls</t>
+  </si>
+  <si>
+    <t>Enjoy a delicious one-pan honey butter salmon &amp; rice recipe that's quick, easy, and full of flavor! Perfect for dinner.</t>
+  </si>
+  <si>
+    <t>Delicious Juicy Air Fryer BBQ Chicken Bites ready in 22 minutes! Perfect appetizer for any gathering. Try them now!</t>
+  </si>
+  <si>
+    <t>Delicious Healthy Greek Chicken Bowls packed with protein, fresh veggies, and flavor. Perfect for a nutritious meal!</t>
+  </si>
+  <si>
+    <t>Indulge in soft &amp; fluffy homemade cinnamon rolls! Perfect for breakfast or dessert, delight in every sweet bite.</t>
+  </si>
+  <si>
+    <t>Honey Glazed Salmon Rice, Sweet Butter Salmon Rice, Honeyed Salmon and Rice</t>
+  </si>
+  <si>
+    <t>Air Fried BBQ Chicken Nuggets, Crispy BBQ Chicken Pieces in Air Fryer, Air Fryer Barbecue Chicken Chunks</t>
+  </si>
+  <si>
+    <t>Nutritious Greek Chicken Bowls, Wholesome Greek Chicken Bowls, Fit Greek Chicken Bowls</t>
+  </si>
+  <si>
+    <t>Homemade Cinnamon Buns, Made-from-Scratch Cinnamon Rolls, DIY Cinnamon Roll Recipe</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>appetizers</t>
+  </si>
+  <si>
+    <t>dessert</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p12-out\output_images\image_1.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p12-out\output_images\image_2.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p12-out\output_images\image_3.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p12-out\output_images\image_4.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,6 +1306,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -328,16 +1347,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -630,10 +1655,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,48 +1677,532 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>56</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V2" t="s">
+        <v>102</v>
+      </c>
+      <c r="W2" t="s">
+        <v>106</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG2">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:36">
       <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V3" t="s">
+        <v>103</v>
+      </c>
+      <c r="W3" t="s">
+        <v>107</v>
+      </c>
+      <c r="X3">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG3">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" t="s">
+        <v>101</v>
+      </c>
+      <c r="V4" t="s">
+        <v>104</v>
+      </c>
+      <c r="W4" t="s">
+        <v>108</v>
+      </c>
+      <c r="X4">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG4">
+        <v>4</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" t="s">
+        <v>80</v>
+      </c>
+      <c r="U5" t="s">
+        <v>101</v>
+      </c>
+      <c r="V5" t="s">
+        <v>105</v>
+      </c>
+      <c r="W5" t="s">
+        <v>109</v>
+      </c>
+      <c r="X5">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG5">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
+      <c r="AH5" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId2"/>
+    <hyperlink ref="I2" r:id="rId3"/>
+    <hyperlink ref="J2" r:id="rId4"/>
+    <hyperlink ref="K2" r:id="rId5"/>
+    <hyperlink ref="N2" r:id="rId6"/>
+    <hyperlink ref="O2" r:id="rId7"/>
+    <hyperlink ref="P2" r:id="rId8"/>
+    <hyperlink ref="Q2" r:id="rId9"/>
+    <hyperlink ref="R2" r:id="rId10"/>
+    <hyperlink ref="G3" r:id="rId11"/>
+    <hyperlink ref="H3" r:id="rId12"/>
+    <hyperlink ref="I3" r:id="rId13"/>
+    <hyperlink ref="J3" r:id="rId14"/>
+    <hyperlink ref="K3" r:id="rId15"/>
+    <hyperlink ref="N3" r:id="rId16"/>
+    <hyperlink ref="O3" r:id="rId17"/>
+    <hyperlink ref="P3" r:id="rId18"/>
+    <hyperlink ref="Q3" r:id="rId19"/>
+    <hyperlink ref="R3" r:id="rId20"/>
+    <hyperlink ref="G4" r:id="rId21"/>
+    <hyperlink ref="H4" r:id="rId22"/>
+    <hyperlink ref="I4" r:id="rId23"/>
+    <hyperlink ref="J4" r:id="rId24"/>
+    <hyperlink ref="K4" r:id="rId25"/>
+    <hyperlink ref="N4" r:id="rId26"/>
+    <hyperlink ref="O4" r:id="rId27"/>
+    <hyperlink ref="P4" r:id="rId28"/>
+    <hyperlink ref="Q4" r:id="rId29"/>
+    <hyperlink ref="R4" r:id="rId30"/>
+    <hyperlink ref="G5" r:id="rId31"/>
+    <hyperlink ref="H5" r:id="rId32"/>
+    <hyperlink ref="I5" r:id="rId33"/>
+    <hyperlink ref="J5" r:id="rId34"/>
+    <hyperlink ref="K5" r:id="rId35"/>
+    <hyperlink ref="N5" r:id="rId36"/>
+    <hyperlink ref="O5" r:id="rId37"/>
+    <hyperlink ref="P5" r:id="rId38"/>
+    <hyperlink ref="Q5" r:id="rId39"/>
+    <hyperlink ref="R5" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>